--- a/grupos/2APV - Estadisticos 20232.xlsx
+++ b/grupos/2APV - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="101">
   <si>
     <t>Materia</t>
   </si>
@@ -176,30 +176,30 @@
     <t>Barañon Samaniego Graciela de los Ángeles</t>
   </si>
   <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
+    <t>Rodríguez Román Leticia</t>
+  </si>
+  <si>
+    <t>De Jesús Orduña Sofía del Pilar</t>
+  </si>
+  <si>
     <t>Hernández Mendoza Delfina</t>
   </si>
   <si>
-    <t>Gaspar Velazco Juan Francisco</t>
+    <t>Contreras Díaz Irma Ivette</t>
+  </si>
+  <si>
+    <t>Pesce Bautista Victor Manuel</t>
+  </si>
+  <si>
+    <t>Sánchez Sánchez Miguel</t>
   </si>
   <si>
     <t>González Nuñez Veronica</t>
   </si>
   <si>
-    <t>De Jesús Orduña Sofía del Pilar</t>
-  </si>
-  <si>
-    <t>Rodríguez Román Leticia</t>
-  </si>
-  <si>
-    <t>Pesce Bautista Victor Manuel</t>
-  </si>
-  <si>
-    <t>Contreras Díaz Irma Ivette</t>
-  </si>
-  <si>
-    <t>Sánchez Sánchez Miguel</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -212,49 +212,55 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>ACOSTA</t>
+  </si>
+  <si>
     <t>AQUINO</t>
   </si>
   <si>
-    <t>CASANOVA</t>
+    <t>BERTELY</t>
   </si>
   <si>
     <t>CORTES</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>IBARRA</t>
+  </si>
+  <si>
+    <t>LUCIANO</t>
+  </si>
+  <si>
     <t>MENDOZA</t>
   </si>
   <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>ACOSTA</t>
-  </si>
-  <si>
-    <t>BERTELY</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>IBARRA</t>
-  </si>
-  <si>
-    <t>LUCIANO</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
     <t>ROMERO</t>
   </si>
   <si>
     <t>ROJAS</t>
   </si>
   <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>-------------</t>
+  </si>
+  <si>
     <t>OLIVARES</t>
   </si>
   <si>
-    <t>CASTILLO</t>
+    <t>GALINDO</t>
   </si>
   <si>
     <t>PEREZ</t>
@@ -263,58 +269,52 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>ZAYAS</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>-------------</t>
-  </si>
-  <si>
-    <t>GALINDO</t>
-  </si>
-  <si>
-    <t>ZAYAS</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
     <t>MUÑOZ</t>
   </si>
   <si>
+    <t>JUSTIN GIOVANNI</t>
+  </si>
+  <si>
+    <t>ILIAN ANELI</t>
+  </si>
+  <si>
     <t>JURISEL</t>
   </si>
   <si>
-    <t>LUCIA</t>
+    <t>MIGUEL</t>
   </si>
   <si>
     <t>DANIEL DE JESUS</t>
   </si>
   <si>
+    <t>MARIEL</t>
+  </si>
+  <si>
+    <t>ARMANDO</t>
+  </si>
+  <si>
+    <t>KEVIN SANTIAGO</t>
+  </si>
+  <si>
     <t>MICHEL LEONEL</t>
   </si>
   <si>
+    <t>CARLOS</t>
+  </si>
+  <si>
     <t>DIEGO</t>
-  </si>
-  <si>
-    <t>ILIAN ANELI</t>
-  </si>
-  <si>
-    <t>MIGUEL</t>
-  </si>
-  <si>
-    <t>MARIEL</t>
-  </si>
-  <si>
-    <t>ARMANDO</t>
-  </si>
-  <si>
-    <t>KEVIN SANTIAGO</t>
-  </si>
-  <si>
-    <t>CARLOS</t>
   </si>
   <si>
     <t>AARON</t>
@@ -904,34 +904,34 @@
         <v>10</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V4">
         <v>-1</v>
@@ -964,7 +964,7 @@
         <v>-1</v>
       </c>
       <c r="AF4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG4">
         <v>6</v>
@@ -976,16 +976,16 @@
         <v>9</v>
       </c>
       <c r="AJ4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AM4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AN4">
         <v>6</v>
@@ -1029,34 +1029,34 @@
         <v>10</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V5">
         <v>-1</v>
@@ -1089,28 +1089,28 @@
         <v>-1</v>
       </c>
       <c r="AF5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG5">
         <v>7</v>
       </c>
       <c r="AH5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ5">
         <v>7</v>
       </c>
       <c r="AK5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AL5">
         <v>8</v>
       </c>
       <c r="AM5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AN5">
         <v>6</v>
@@ -1154,34 +1154,34 @@
         <v>10</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V6">
         <v>-1</v>
@@ -1223,16 +1223,16 @@
         <v>7</v>
       </c>
       <c r="AI6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK6">
         <v>5</v>
       </c>
       <c r="AL6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AM6">
         <v>5</v>
@@ -1279,34 +1279,34 @@
         <v>5</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V7">
         <v>-1</v>
@@ -1339,7 +1339,7 @@
         <v>-1</v>
       </c>
       <c r="AF7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG7">
         <v>5</v>
@@ -1348,19 +1348,19 @@
         <v>5</v>
       </c>
       <c r="AI7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AJ7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AM7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AN7">
         <v>5</v>
@@ -1404,34 +1404,34 @@
         <v>10</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V8">
         <v>-1</v>
@@ -1464,7 +1464,7 @@
         <v>-1</v>
       </c>
       <c r="AF8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG8">
         <v>6</v>
@@ -1476,16 +1476,16 @@
         <v>9</v>
       </c>
       <c r="AJ8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AL8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AM8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AN8">
         <v>6</v>
@@ -1529,34 +1529,34 @@
         <v>10</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V9">
         <v>-1</v>
@@ -1592,16 +1592,16 @@
         <v>7</v>
       </c>
       <c r="AG9">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AH9">
         <v>7</v>
       </c>
       <c r="AI9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK9">
         <v>6</v>
@@ -1610,7 +1610,7 @@
         <v>6</v>
       </c>
       <c r="AM9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AN9">
         <v>5</v>
@@ -1654,34 +1654,34 @@
         <v>10</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V10">
         <v>-1</v>
@@ -1723,7 +1723,7 @@
         <v>5</v>
       </c>
       <c r="AI10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ10">
         <v>7</v>
@@ -1732,7 +1732,7 @@
         <v>5</v>
       </c>
       <c r="AL10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AM10">
         <v>6</v>
@@ -1779,34 +1779,34 @@
         <v>10</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V11">
         <v>-1</v>
@@ -1839,28 +1839,28 @@
         <v>-1</v>
       </c>
       <c r="AF11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI11">
         <v>7</v>
       </c>
       <c r="AJ11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AK11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL11">
         <v>7</v>
       </c>
       <c r="AM11">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AN11">
         <v>6</v>
@@ -1904,34 +1904,34 @@
         <v>10</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V12">
         <v>-1</v>
@@ -1964,13 +1964,13 @@
         <v>-1</v>
       </c>
       <c r="AF12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG12">
         <v>7</v>
       </c>
       <c r="AH12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI12">
         <v>8</v>
@@ -2029,34 +2029,34 @@
         <v>10</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V13">
         <v>-1</v>
@@ -2089,7 +2089,7 @@
         <v>-1</v>
       </c>
       <c r="AF13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG13">
         <v>5</v>
@@ -2101,7 +2101,7 @@
         <v>5</v>
       </c>
       <c r="AJ13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK13">
         <v>5</v>
@@ -2113,7 +2113,7 @@
         <v>5</v>
       </c>
       <c r="AN13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AO13">
         <v>-1</v>
@@ -2154,34 +2154,34 @@
         <v>10</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V14">
         <v>-1</v>
@@ -2220,7 +2220,7 @@
         <v>6</v>
       </c>
       <c r="AH14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI14">
         <v>5</v>
@@ -2229,13 +2229,13 @@
         <v>7</v>
       </c>
       <c r="AK14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL14">
         <v>5</v>
       </c>
       <c r="AM14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AN14">
         <v>5</v>
@@ -2279,34 +2279,34 @@
         <v>10</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V15">
         <v>-1</v>
@@ -2357,7 +2357,7 @@
         <v>6</v>
       </c>
       <c r="AL15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AM15">
         <v>5</v>
@@ -2404,34 +2404,34 @@
         <v>10</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V16">
         <v>-1</v>
@@ -2470,7 +2470,7 @@
         <v>6</v>
       </c>
       <c r="AH16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI16">
         <v>6</v>
@@ -2479,13 +2479,13 @@
         <v>10</v>
       </c>
       <c r="AK16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL16">
         <v>8</v>
       </c>
       <c r="AM16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AN16">
         <v>6</v>
@@ -2529,34 +2529,34 @@
         <v>5</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V17">
         <v>-1</v>
@@ -2598,19 +2598,19 @@
         <v>5</v>
       </c>
       <c r="AI17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK17">
         <v>5</v>
       </c>
       <c r="AL17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AM17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AN17">
         <v>5</v>
@@ -2654,34 +2654,34 @@
         <v>10</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V18">
         <v>-1</v>
@@ -2714,19 +2714,19 @@
         <v>-1</v>
       </c>
       <c r="AF18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AK18">
         <v>7</v>
@@ -2735,7 +2735,7 @@
         <v>7</v>
       </c>
       <c r="AM18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AN18">
         <v>6</v>
@@ -2779,34 +2779,34 @@
         <v>10</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V19">
         <v>-1</v>
@@ -2848,7 +2848,7 @@
         <v>7</v>
       </c>
       <c r="AI19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ19">
         <v>8</v>
@@ -2860,7 +2860,7 @@
         <v>7</v>
       </c>
       <c r="AM19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AN19">
         <v>6</v>
@@ -2904,34 +2904,34 @@
         <v>10</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V20">
         <v>-1</v>
@@ -2970,10 +2970,10 @@
         <v>8</v>
       </c>
       <c r="AH20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ20">
         <v>8</v>
@@ -2985,7 +2985,7 @@
         <v>9</v>
       </c>
       <c r="AM20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AN20">
         <v>6</v>
@@ -3029,34 +3029,34 @@
         <v>10</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V21">
         <v>-1</v>
@@ -3089,7 +3089,7 @@
         <v>-1</v>
       </c>
       <c r="AF21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG21">
         <v>6</v>
@@ -3101,16 +3101,16 @@
         <v>9</v>
       </c>
       <c r="AJ21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK21">
         <v>5</v>
       </c>
       <c r="AL21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AM21">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AN21">
         <v>6</v>
@@ -3154,34 +3154,34 @@
         <v>10</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V22">
         <v>-1</v>
@@ -3220,19 +3220,19 @@
         <v>5</v>
       </c>
       <c r="AH22">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AI22">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AJ22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AM22">
         <v>5</v>
@@ -3279,34 +3279,34 @@
         <v>10</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V23">
         <v>-1</v>
@@ -3339,7 +3339,7 @@
         <v>-1</v>
       </c>
       <c r="AF23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG23">
         <v>7</v>
@@ -3348,19 +3348,19 @@
         <v>9</v>
       </c>
       <c r="AI23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AJ23">
         <v>9</v>
       </c>
       <c r="AK23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AL23">
         <v>8</v>
       </c>
       <c r="AM23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AN23">
         <v>6</v>
@@ -3404,34 +3404,34 @@
         <v>10</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V24">
         <v>-1</v>
@@ -3464,22 +3464,22 @@
         <v>-1</v>
       </c>
       <c r="AF24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG24">
         <v>7</v>
       </c>
       <c r="AH24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI24">
         <v>8</v>
       </c>
       <c r="AJ24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL24">
         <v>9</v>
@@ -3529,34 +3529,34 @@
         <v>10</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V25">
         <v>-1</v>
@@ -3589,7 +3589,7 @@
         <v>-1</v>
       </c>
       <c r="AF25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG25">
         <v>9</v>
@@ -3613,7 +3613,7 @@
         <v>7</v>
       </c>
       <c r="AN25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO25">
         <v>-1</v>
@@ -3654,34 +3654,34 @@
         <v>10</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V26">
         <v>-1</v>
@@ -3729,13 +3729,13 @@
         <v>7</v>
       </c>
       <c r="AK26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AL26">
         <v>7</v>
       </c>
       <c r="AM26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AN26">
         <v>5</v>
@@ -3940,10 +3940,10 @@
         <v>100</v>
       </c>
       <c r="M4">
-        <v>91.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="N4">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="O4">
         <v>100</v>
@@ -3961,7 +3961,7 @@
         <v>100</v>
       </c>
       <c r="T4">
-        <v>90</v>
+        <v>95.3</v>
       </c>
       <c r="U4">
         <v>100</v>
@@ -3970,10 +3970,10 @@
         <v>100</v>
       </c>
       <c r="W4">
-        <v>91.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="X4">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="Y4">
         <v>100</v>
@@ -3991,7 +3991,7 @@
         <v>100</v>
       </c>
       <c r="AD4">
-        <v>90</v>
+        <v>95.3</v>
       </c>
       <c r="AE4">
         <v>100</v>
@@ -4032,13 +4032,13 @@
         <v>100</v>
       </c>
       <c r="L5">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="M5">
-        <v>83.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="N5">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="O5">
         <v>100</v>
@@ -4053,22 +4053,22 @@
         <v>100</v>
       </c>
       <c r="S5">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="T5">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="U5">
         <v>100</v>
       </c>
       <c r="V5">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="W5">
-        <v>83.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="X5">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="Y5">
         <v>100</v>
@@ -4083,10 +4083,10 @@
         <v>100</v>
       </c>
       <c r="AC5">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="AD5">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="AE5">
         <v>100</v>
@@ -4127,10 +4127,10 @@
         <v>100</v>
       </c>
       <c r="L6">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="M6">
-        <v>100</v>
+        <v>81.8</v>
       </c>
       <c r="N6">
         <v>100</v>
@@ -4139,28 +4139,28 @@
         <v>100</v>
       </c>
       <c r="P6">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="Q6">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="R6">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="S6">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="T6">
-        <v>85</v>
+        <v>83.7</v>
       </c>
       <c r="U6">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="V6">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="W6">
-        <v>100</v>
+        <v>81.8</v>
       </c>
       <c r="X6">
         <v>100</v>
@@ -4169,22 +4169,22 @@
         <v>100</v>
       </c>
       <c r="Z6">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AA6">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="AB6">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="AC6">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="AD6">
-        <v>85</v>
+        <v>83.7</v>
       </c>
       <c r="AE6">
-        <v>100</v>
+        <v>96.7</v>
       </c>
     </row>
     <row r="7" spans="1:31">
@@ -4222,10 +4222,10 @@
         <v>66.7</v>
       </c>
       <c r="L7">
-        <v>42.9</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="M7">
-        <v>75</v>
+        <v>77.3</v>
       </c>
       <c r="N7">
         <v>75</v>
@@ -4234,28 +4234,28 @@
         <v>100</v>
       </c>
       <c r="P7">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="Q7">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="R7">
-        <v>81.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S7">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T7">
-        <v>70</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="U7">
-        <v>66.7</v>
+        <v>76.7</v>
       </c>
       <c r="V7">
-        <v>42.9</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="W7">
-        <v>75</v>
+        <v>77.3</v>
       </c>
       <c r="X7">
         <v>75</v>
@@ -4264,22 +4264,22 @@
         <v>100</v>
       </c>
       <c r="Z7">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AA7">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="AB7">
-        <v>81.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="AC7">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AD7">
-        <v>70</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="AE7">
-        <v>66.7</v>
+        <v>76.7</v>
       </c>
     </row>
     <row r="8" spans="1:31">
@@ -4341,7 +4341,7 @@
         <v>100</v>
       </c>
       <c r="T8">
-        <v>90</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="U8">
         <v>100</v>
@@ -4371,7 +4371,7 @@
         <v>100</v>
       </c>
       <c r="AD8">
-        <v>90</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="AE8">
         <v>100</v>
@@ -4412,13 +4412,13 @@
         <v>100</v>
       </c>
       <c r="L9">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="M9">
-        <v>100</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="N9">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="O9">
         <v>100</v>
@@ -4427,28 +4427,28 @@
         <v>100</v>
       </c>
       <c r="Q9">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="R9">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S9">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="T9">
-        <v>100</v>
+        <v>83.7</v>
       </c>
       <c r="U9">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="V9">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="W9">
-        <v>100</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="X9">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="Y9">
         <v>100</v>
@@ -4457,19 +4457,19 @@
         <v>100</v>
       </c>
       <c r="AA9">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="AB9">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AC9">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="AD9">
-        <v>100</v>
+        <v>83.7</v>
       </c>
       <c r="AE9">
-        <v>100</v>
+        <v>93.3</v>
       </c>
     </row>
     <row r="10" spans="1:31">
@@ -4507,64 +4507,64 @@
         <v>100</v>
       </c>
       <c r="L10">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="M10">
-        <v>83.3</v>
+        <v>72.7</v>
       </c>
       <c r="N10">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="O10">
         <v>100</v>
       </c>
       <c r="P10">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="Q10">
         <v>88</v>
       </c>
       <c r="R10">
-        <v>81.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S10">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T10">
-        <v>70</v>
+        <v>69.8</v>
       </c>
       <c r="U10">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="V10">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="W10">
-        <v>83.3</v>
+        <v>72.7</v>
       </c>
       <c r="X10">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="Y10">
         <v>100</v>
       </c>
       <c r="Z10">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AA10">
         <v>88</v>
       </c>
       <c r="AB10">
-        <v>81.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="AC10">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AD10">
-        <v>70</v>
+        <v>69.8</v>
       </c>
       <c r="AE10">
-        <v>100</v>
+        <v>93.3</v>
       </c>
     </row>
     <row r="11" spans="1:31">
@@ -4605,7 +4605,7 @@
         <v>100</v>
       </c>
       <c r="M11">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="N11">
         <v>100</v>
@@ -4623,10 +4623,10 @@
         <v>100</v>
       </c>
       <c r="S11">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T11">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="U11">
         <v>100</v>
@@ -4635,7 +4635,7 @@
         <v>100</v>
       </c>
       <c r="W11">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="X11">
         <v>100</v>
@@ -4653,10 +4653,10 @@
         <v>100</v>
       </c>
       <c r="AC11">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AD11">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AE11">
         <v>100</v>
@@ -4700,10 +4700,10 @@
         <v>100</v>
       </c>
       <c r="M12">
-        <v>83.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="N12">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="O12">
         <v>100</v>
@@ -4721,7 +4721,7 @@
         <v>100</v>
       </c>
       <c r="T12">
-        <v>85</v>
+        <v>95.3</v>
       </c>
       <c r="U12">
         <v>100</v>
@@ -4730,10 +4730,10 @@
         <v>100</v>
       </c>
       <c r="W12">
-        <v>83.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="X12">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="Y12">
         <v>100</v>
@@ -4751,7 +4751,7 @@
         <v>100</v>
       </c>
       <c r="AD12">
-        <v>85</v>
+        <v>95.3</v>
       </c>
       <c r="AE12">
         <v>100</v>
@@ -4795,61 +4795,61 @@
         <v>80</v>
       </c>
       <c r="M13">
-        <v>91.7</v>
+        <v>50</v>
       </c>
       <c r="N13">
-        <v>75</v>
+        <v>52.5</v>
       </c>
       <c r="O13">
         <v>50</v>
       </c>
       <c r="P13">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="Q13">
         <v>60</v>
       </c>
       <c r="R13">
-        <v>81.3</v>
+        <v>75</v>
       </c>
       <c r="S13">
-        <v>87.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="T13">
-        <v>65</v>
+        <v>53.5</v>
       </c>
       <c r="U13">
-        <v>100</v>
+        <v>56.7</v>
       </c>
       <c r="V13">
         <v>80</v>
       </c>
       <c r="W13">
-        <v>91.7</v>
+        <v>50</v>
       </c>
       <c r="X13">
-        <v>75</v>
+        <v>52.5</v>
       </c>
       <c r="Y13">
         <v>50</v>
       </c>
       <c r="Z13">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AA13">
         <v>60</v>
       </c>
       <c r="AB13">
-        <v>81.3</v>
+        <v>75</v>
       </c>
       <c r="AC13">
-        <v>87.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="AD13">
-        <v>65</v>
+        <v>53.5</v>
       </c>
       <c r="AE13">
-        <v>100</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="14" spans="1:31">
@@ -4890,7 +4890,7 @@
         <v>97.09999999999999</v>
       </c>
       <c r="M14">
-        <v>83.3</v>
+        <v>77.3</v>
       </c>
       <c r="N14">
         <v>85</v>
@@ -4902,25 +4902,25 @@
         <v>96</v>
       </c>
       <c r="Q14">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="R14">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="S14">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="T14">
-        <v>80</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="U14">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="V14">
         <v>97.09999999999999</v>
       </c>
       <c r="W14">
-        <v>83.3</v>
+        <v>77.3</v>
       </c>
       <c r="X14">
         <v>85</v>
@@ -4932,19 +4932,19 @@
         <v>96</v>
       </c>
       <c r="AA14">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="AB14">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="AC14">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="AD14">
-        <v>80</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="AE14">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:31">
@@ -4982,13 +4982,13 @@
         <v>80</v>
       </c>
       <c r="L15">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="M15">
-        <v>100</v>
+        <v>77.3</v>
       </c>
       <c r="N15">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="O15">
         <v>100</v>
@@ -5003,22 +5003,22 @@
         <v>100</v>
       </c>
       <c r="S15">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T15">
-        <v>95</v>
+        <v>83.7</v>
       </c>
       <c r="U15">
-        <v>80</v>
+        <v>83.3</v>
       </c>
       <c r="V15">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="W15">
-        <v>100</v>
+        <v>77.3</v>
       </c>
       <c r="X15">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="Y15">
         <v>100</v>
@@ -5033,13 +5033,13 @@
         <v>100</v>
       </c>
       <c r="AC15">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AD15">
-        <v>95</v>
+        <v>83.7</v>
       </c>
       <c r="AE15">
-        <v>80</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="16" spans="1:31">
@@ -5083,7 +5083,7 @@
         <v>100</v>
       </c>
       <c r="N16">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="O16">
         <v>100</v>
@@ -5101,7 +5101,7 @@
         <v>100</v>
       </c>
       <c r="T16">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="U16">
         <v>100</v>
@@ -5113,7 +5113,7 @@
         <v>100</v>
       </c>
       <c r="X16">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="Y16">
         <v>100</v>
@@ -5131,7 +5131,7 @@
         <v>100</v>
       </c>
       <c r="AD16">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="AE16">
         <v>100</v>
@@ -5172,64 +5172,64 @@
         <v>66.7</v>
       </c>
       <c r="L17">
-        <v>62.9</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="M17">
-        <v>91.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="N17">
-        <v>75</v>
+        <v>77.5</v>
       </c>
       <c r="O17">
         <v>100</v>
       </c>
       <c r="P17">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="Q17">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="R17">
-        <v>81.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S17">
-        <v>81.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="T17">
-        <v>60</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="U17">
-        <v>66.7</v>
+        <v>83.3</v>
       </c>
       <c r="V17">
-        <v>62.9</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="W17">
-        <v>91.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="X17">
-        <v>75</v>
+        <v>77.5</v>
       </c>
       <c r="Y17">
         <v>100</v>
       </c>
       <c r="Z17">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AA17">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="AB17">
-        <v>81.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="AC17">
-        <v>81.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="AD17">
-        <v>60</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="AE17">
-        <v>66.7</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="18" spans="1:31">
@@ -5267,61 +5267,61 @@
         <v>100</v>
       </c>
       <c r="L18">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="M18">
         <v>100</v>
       </c>
       <c r="N18">
-        <v>95</v>
+        <v>87.5</v>
       </c>
       <c r="O18">
         <v>100</v>
       </c>
       <c r="P18">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="Q18">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="R18">
-        <v>93.8</v>
+        <v>81.3</v>
       </c>
       <c r="S18">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T18">
-        <v>95</v>
+        <v>90.7</v>
       </c>
       <c r="U18">
         <v>100</v>
       </c>
       <c r="V18">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="W18">
         <v>100</v>
       </c>
       <c r="X18">
-        <v>95</v>
+        <v>87.5</v>
       </c>
       <c r="Y18">
         <v>100</v>
       </c>
       <c r="Z18">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AA18">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="AB18">
-        <v>93.8</v>
+        <v>81.3</v>
       </c>
       <c r="AC18">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AD18">
-        <v>95</v>
+        <v>90.7</v>
       </c>
       <c r="AE18">
         <v>100</v>
@@ -5365,7 +5365,7 @@
         <v>100</v>
       </c>
       <c r="M19">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N19">
         <v>100</v>
@@ -5386,7 +5386,7 @@
         <v>100</v>
       </c>
       <c r="T19">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="U19">
         <v>100</v>
@@ -5395,7 +5395,7 @@
         <v>100</v>
       </c>
       <c r="W19">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="X19">
         <v>100</v>
@@ -5416,7 +5416,7 @@
         <v>100</v>
       </c>
       <c r="AD19">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="AE19">
         <v>100</v>
@@ -5460,10 +5460,10 @@
         <v>100</v>
       </c>
       <c r="M20">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="N20">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="O20">
         <v>100</v>
@@ -5472,7 +5472,7 @@
         <v>100</v>
       </c>
       <c r="Q20">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="R20">
         <v>100</v>
@@ -5481,7 +5481,7 @@
         <v>100</v>
       </c>
       <c r="T20">
-        <v>85</v>
+        <v>95.3</v>
       </c>
       <c r="U20">
         <v>100</v>
@@ -5490,10 +5490,10 @@
         <v>100</v>
       </c>
       <c r="W20">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="X20">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="Y20">
         <v>100</v>
@@ -5502,7 +5502,7 @@
         <v>100</v>
       </c>
       <c r="AA20">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="AB20">
         <v>100</v>
@@ -5511,7 +5511,7 @@
         <v>100</v>
       </c>
       <c r="AD20">
-        <v>85</v>
+        <v>95.3</v>
       </c>
       <c r="AE20">
         <v>100</v>
@@ -5555,19 +5555,19 @@
         <v>100</v>
       </c>
       <c r="M21">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N21">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="O21">
         <v>100</v>
       </c>
       <c r="P21">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="Q21">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="R21">
         <v>100</v>
@@ -5576,7 +5576,7 @@
         <v>100</v>
       </c>
       <c r="T21">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="U21">
         <v>100</v>
@@ -5585,19 +5585,19 @@
         <v>100</v>
       </c>
       <c r="W21">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="X21">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="Y21">
         <v>100</v>
       </c>
       <c r="Z21">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AA21">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="AB21">
         <v>100</v>
@@ -5606,7 +5606,7 @@
         <v>100</v>
       </c>
       <c r="AD21">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AE21">
         <v>100</v>
@@ -5647,64 +5647,64 @@
         <v>100</v>
       </c>
       <c r="L22">
-        <v>94.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="M22">
-        <v>91.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="N22">
-        <v>95</v>
+        <v>92.5</v>
       </c>
       <c r="O22">
         <v>100</v>
       </c>
       <c r="P22">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="Q22">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="R22">
-        <v>81.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S22">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T22">
-        <v>85</v>
+        <v>83.7</v>
       </c>
       <c r="U22">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="V22">
-        <v>94.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="W22">
-        <v>91.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="X22">
-        <v>95</v>
+        <v>92.5</v>
       </c>
       <c r="Y22">
         <v>100</v>
       </c>
       <c r="Z22">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AA22">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AB22">
-        <v>81.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="AC22">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AD22">
-        <v>85</v>
+        <v>83.7</v>
       </c>
       <c r="AE22">
-        <v>100</v>
+        <v>93.3</v>
       </c>
     </row>
     <row r="23" spans="1:31">
@@ -5745,7 +5745,7 @@
         <v>100</v>
       </c>
       <c r="M23">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N23">
         <v>100</v>
@@ -5760,22 +5760,22 @@
         <v>100</v>
       </c>
       <c r="R23">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S23">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T23">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="U23">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="V23">
         <v>100</v>
       </c>
       <c r="W23">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="X23">
         <v>100</v>
@@ -5790,16 +5790,16 @@
         <v>100</v>
       </c>
       <c r="AB23">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AC23">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AD23">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="AE23">
-        <v>100</v>
+        <v>93.3</v>
       </c>
     </row>
     <row r="24" spans="1:31">
@@ -5843,7 +5843,7 @@
         <v>100</v>
       </c>
       <c r="N24">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="O24">
         <v>100</v>
@@ -5858,10 +5858,10 @@
         <v>100</v>
       </c>
       <c r="S24">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T24">
-        <v>85</v>
+        <v>90.7</v>
       </c>
       <c r="U24">
         <v>100</v>
@@ -5873,7 +5873,7 @@
         <v>100</v>
       </c>
       <c r="X24">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="Y24">
         <v>100</v>
@@ -5888,10 +5888,10 @@
         <v>100</v>
       </c>
       <c r="AC24">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AD24">
-        <v>85</v>
+        <v>90.7</v>
       </c>
       <c r="AE24">
         <v>100</v>
@@ -5953,10 +5953,10 @@
         <v>100</v>
       </c>
       <c r="S25">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T25">
-        <v>95</v>
+        <v>97.7</v>
       </c>
       <c r="U25">
         <v>100</v>
@@ -5983,10 +5983,10 @@
         <v>100</v>
       </c>
       <c r="AC25">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AD25">
-        <v>95</v>
+        <v>97.7</v>
       </c>
       <c r="AE25">
         <v>100</v>
@@ -6030,7 +6030,7 @@
         <v>100</v>
       </c>
       <c r="M26">
-        <v>75</v>
+        <v>81.8</v>
       </c>
       <c r="N26">
         <v>100</v>
@@ -6042,16 +6042,16 @@
         <v>100</v>
       </c>
       <c r="Q26">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R26">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S26">
         <v>100</v>
       </c>
       <c r="T26">
-        <v>65</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="U26">
         <v>100</v>
@@ -6060,7 +6060,7 @@
         <v>100</v>
       </c>
       <c r="W26">
-        <v>75</v>
+        <v>81.8</v>
       </c>
       <c r="X26">
         <v>100</v>
@@ -6072,16 +6072,16 @@
         <v>100</v>
       </c>
       <c r="AA26">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AB26">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AC26">
         <v>100</v>
       </c>
       <c r="AD26">
-        <v>65</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="AE26">
         <v>100</v>
@@ -6170,7 +6170,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>52</v>
@@ -6179,19 +6179,19 @@
         <v>23</v>
       </c>
       <c r="D3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" s="2">
-        <v>56.5</v>
+        <v>60.9</v>
       </c>
       <c r="G3" s="2">
-        <v>43.5</v>
+        <v>39.1</v>
       </c>
       <c r="H3">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6202,7 +6202,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
         <v>53</v>
@@ -6211,19 +6211,19 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" s="2">
-        <v>65.2</v>
+        <v>60.9</v>
       </c>
       <c r="G4" s="2">
-        <v>34.8</v>
+        <v>39.1</v>
       </c>
       <c r="H4">
-        <v>6.3</v>
+        <v>5.7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6234,7 +6234,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>54</v>
@@ -6243,19 +6243,19 @@
         <v>23</v>
       </c>
       <c r="D5">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F5" s="2">
-        <v>65.2</v>
+        <v>78.3</v>
       </c>
       <c r="G5" s="2">
-        <v>34.8</v>
+        <v>21.7</v>
       </c>
       <c r="H5">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6266,7 +6266,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
         <v>55</v>
@@ -6275,19 +6275,19 @@
         <v>23</v>
       </c>
       <c r="D6">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F6" s="2">
-        <v>65.2</v>
+        <v>78.3</v>
       </c>
       <c r="G6" s="2">
-        <v>34.8</v>
+        <v>21.7</v>
       </c>
       <c r="H6">
-        <v>6.2</v>
+        <v>7.3</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6298,7 +6298,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
         <v>56</v>
@@ -6307,19 +6307,19 @@
         <v>23</v>
       </c>
       <c r="D7">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E7">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F7" s="2">
-        <v>65.2</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="G7" s="2">
-        <v>34.8</v>
+        <v>17.4</v>
       </c>
       <c r="H7">
-        <v>5.7</v>
+        <v>7.7</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6339,19 +6339,19 @@
         <v>23</v>
       </c>
       <c r="D8">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E8">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F8" s="2">
-        <v>69.59999999999999</v>
+        <v>91.3</v>
       </c>
       <c r="G8" s="2">
-        <v>30.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H8">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -6362,7 +6362,7 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B9" t="s">
         <v>58</v>
@@ -6371,16 +6371,16 @@
         <v>23</v>
       </c>
       <c r="D9">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F9" s="2">
-        <v>82.59999999999999</v>
+        <v>91.3</v>
       </c>
       <c r="G9" s="2">
-        <v>17.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H9">
         <v>7.6</v>
@@ -6394,7 +6394,7 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s">
         <v>59</v>
@@ -6415,7 +6415,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="H10">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -6429,25 +6429,25 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C11">
         <v>23</v>
       </c>
       <c r="D11">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" s="2">
-        <v>91.3</v>
+        <v>95.7</v>
       </c>
       <c r="G11" s="2">
-        <v>8.699999999999999</v>
+        <v>4.3</v>
       </c>
       <c r="H11">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -6497,7 +6497,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6529,7 +6529,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920281</v>
+        <v>23330051920308</v>
       </c>
       <c r="B2" t="s">
         <v>64</v>
@@ -6541,10 +6541,10 @@
         <v>88</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -6552,7 +6552,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920281</v>
+        <v>23330051920308</v>
       </c>
       <c r="B3" t="s">
         <v>64</v>
@@ -6575,7 +6575,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920347</v>
+        <v>23330051920322</v>
       </c>
       <c r="B4" t="s">
         <v>65</v>
@@ -6587,27 +6587,27 @@
         <v>89</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920347</v>
+        <v>23330051920281</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E5" t="s">
         <v>14</v>
@@ -6621,25 +6621,25 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920285</v>
+        <v>23330051920284</v>
       </c>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -6647,13 +6647,13 @@
         <v>23330051920285</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D7" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E7" t="s">
         <v>14</v>
@@ -6667,39 +6667,39 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920299</v>
+        <v>23330051920292</v>
       </c>
       <c r="B8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D8" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G8">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920299</v>
+        <v>23330051920295</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D9" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E9" t="s">
         <v>14</v>
@@ -6713,39 +6713,39 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920348</v>
+        <v>23330051920296</v>
       </c>
       <c r="B10" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D10" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F10" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="G10">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920348</v>
+        <v>23330051920299</v>
       </c>
       <c r="B11" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D11" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E11" t="s">
         <v>14</v>
@@ -6759,16 +6759,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920322</v>
+        <v>23330051920301</v>
       </c>
       <c r="B12" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C12" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="D12" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="E12" t="s">
         <v>14</v>
@@ -6782,16 +6782,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920284</v>
+        <v>23330051920348</v>
       </c>
       <c r="B13" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C13" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D13" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E13" t="s">
         <v>14</v>
@@ -6805,16 +6805,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920292</v>
+        <v>23330051920363</v>
       </c>
       <c r="B14" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C14" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="D14" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E14" t="s">
         <v>14</v>
@@ -6828,16 +6828,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920295</v>
+        <v>23330051920326</v>
       </c>
       <c r="B15" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C15" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D15" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E15" t="s">
         <v>14</v>
@@ -6846,98 +6846,6 @@
         <v>51</v>
       </c>
       <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>23330051920296</v>
-      </c>
-      <c r="B16" t="s">
-        <v>73</v>
-      </c>
-      <c r="C16" t="s">
-        <v>85</v>
-      </c>
-      <c r="D16" t="s">
-        <v>97</v>
-      </c>
-      <c r="E16" t="s">
-        <v>14</v>
-      </c>
-      <c r="F16" t="s">
-        <v>51</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>23330051920301</v>
-      </c>
-      <c r="B17" t="s">
-        <v>74</v>
-      </c>
-      <c r="C17" t="s">
-        <v>66</v>
-      </c>
-      <c r="D17" t="s">
-        <v>98</v>
-      </c>
-      <c r="E17" t="s">
-        <v>14</v>
-      </c>
-      <c r="F17" t="s">
-        <v>51</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>23330051920363</v>
-      </c>
-      <c r="B18" t="s">
-        <v>75</v>
-      </c>
-      <c r="C18" t="s">
-        <v>86</v>
-      </c>
-      <c r="D18" t="s">
-        <v>99</v>
-      </c>
-      <c r="E18" t="s">
-        <v>14</v>
-      </c>
-      <c r="F18" t="s">
-        <v>51</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>23330051920326</v>
-      </c>
-      <c r="B19" t="s">
-        <v>76</v>
-      </c>
-      <c r="C19" t="s">
-        <v>87</v>
-      </c>
-      <c r="D19" t="s">
-        <v>100</v>
-      </c>
-      <c r="E19" t="s">
-        <v>14</v>
-      </c>
-      <c r="F19" t="s">
-        <v>51</v>
-      </c>
-      <c r="G19">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/2APV - Estadisticos 20232.xlsx
+++ b/grupos/2APV - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="107">
   <si>
     <t>Materia</t>
   </si>
@@ -176,30 +176,30 @@
     <t>Barañon Samaniego Graciela de los Ángeles</t>
   </si>
   <si>
+    <t>Rodríguez Román Leticia</t>
+  </si>
+  <si>
     <t>Gaspar Velazco Juan Francisco</t>
   </si>
   <si>
-    <t>Rodríguez Román Leticia</t>
+    <t>González Nuñez Veronica</t>
+  </si>
+  <si>
+    <t>Hernández Mendoza Delfina</t>
+  </si>
+  <si>
+    <t>Pesce Bautista Victor Manuel</t>
+  </si>
+  <si>
+    <t>Contreras Díaz Irma Ivette</t>
+  </si>
+  <si>
+    <t>Sánchez Sánchez Miguel</t>
   </si>
   <si>
     <t>De Jesús Orduña Sofía del Pilar</t>
   </si>
   <si>
-    <t>Hernández Mendoza Delfina</t>
-  </si>
-  <si>
-    <t>Contreras Díaz Irma Ivette</t>
-  </si>
-  <si>
-    <t>Pesce Bautista Victor Manuel</t>
-  </si>
-  <si>
-    <t>Sánchez Sánchez Miguel</t>
-  </si>
-  <si>
-    <t>González Nuñez Veronica</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -212,34 +212,40 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>ACOSTA</t>
+  </si>
+  <si>
+    <t>AQUINO</t>
+  </si>
+  <si>
+    <t>BERTELY</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>IBARRA</t>
+  </si>
+  <si>
+    <t>LUCIANO</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
     <t>PALOMARES</t>
   </si>
   <si>
-    <t>ACOSTA</t>
-  </si>
-  <si>
-    <t>AQUINO</t>
-  </si>
-  <si>
-    <t>BERTELY</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>IBARRA</t>
-  </si>
-  <si>
-    <t>LUCIANO</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
+    <t>PELAYO</t>
   </si>
   <si>
     <t>RODRIGUEZ</t>
@@ -251,28 +257,34 @@
     <t>ROJAS</t>
   </si>
   <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>-------------</t>
+  </si>
+  <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>GALINDO</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>ZAYAS</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>-------------</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>GALINDO</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>ZAYAS</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
+    <t>TORRES</t>
   </si>
   <si>
     <t>LOPEZ</t>
@@ -284,34 +296,40 @@
     <t>MUÑOZ</t>
   </si>
   <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>ILIAN ANELI</t>
+  </si>
+  <si>
+    <t>JURISEL</t>
+  </si>
+  <si>
+    <t>MIGUEL</t>
+  </si>
+  <si>
+    <t>DANIEL DE JESUS</t>
+  </si>
+  <si>
+    <t>MARIEL</t>
+  </si>
+  <si>
+    <t>ARMANDO</t>
+  </si>
+  <si>
+    <t>KEVIN SANTIAGO</t>
+  </si>
+  <si>
+    <t>MICHEL LEONEL</t>
+  </si>
+  <si>
+    <t>CARLOS</t>
+  </si>
+  <si>
     <t>JUSTIN GIOVANNI</t>
   </si>
   <si>
-    <t>ILIAN ANELI</t>
-  </si>
-  <si>
-    <t>JURISEL</t>
-  </si>
-  <si>
-    <t>MIGUEL</t>
-  </si>
-  <si>
-    <t>DANIEL DE JESUS</t>
-  </si>
-  <si>
-    <t>MARIEL</t>
-  </si>
-  <si>
-    <t>ARMANDO</t>
-  </si>
-  <si>
-    <t>KEVIN SANTIAGO</t>
-  </si>
-  <si>
-    <t>MICHEL LEONEL</t>
-  </si>
-  <si>
-    <t>CARLOS</t>
+    <t>IVAN JESUS</t>
   </si>
   <si>
     <t>DIEGO</t>
@@ -934,34 +952,34 @@
         <v>10</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AD4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AE4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AF4">
         <v>8</v>
@@ -976,16 +994,16 @@
         <v>9</v>
       </c>
       <c r="AJ4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL4">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AM4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AN4">
         <v>6</v>
@@ -1059,43 +1077,43 @@
         <v>10</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AD5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AE5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AF5">
         <v>8</v>
       </c>
       <c r="AG5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AI5">
         <v>7</v>
@@ -1107,7 +1125,7 @@
         <v>7</v>
       </c>
       <c r="AL5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AM5">
         <v>6</v>
@@ -1184,34 +1202,34 @@
         <v>10</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W6">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="X6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AD6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AE6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AF6">
         <v>7</v>
@@ -1220,16 +1238,16 @@
         <v>5</v>
       </c>
       <c r="AH6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI6">
         <v>7</v>
       </c>
       <c r="AJ6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL6">
         <v>6</v>
@@ -1309,34 +1327,34 @@
         <v>10</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AD7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AE7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AF7">
         <v>6</v>
@@ -1345,7 +1363,7 @@
         <v>5</v>
       </c>
       <c r="AH7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AI7">
         <v>7</v>
@@ -1434,34 +1452,34 @@
         <v>10</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AD8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AE8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AF8">
         <v>8</v>
@@ -1482,10 +1500,10 @@
         <v>7</v>
       </c>
       <c r="AL8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AM8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AN8">
         <v>6</v>
@@ -1559,34 +1577,34 @@
         <v>10</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="X9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AD9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AE9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AF9">
         <v>7</v>
@@ -1601,16 +1619,16 @@
         <v>7</v>
       </c>
       <c r="AJ9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK9">
         <v>6</v>
       </c>
       <c r="AL9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AM9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AN9">
         <v>5</v>
@@ -1684,55 +1702,55 @@
         <v>10</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AD10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AE10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AF10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG10">
         <v>5</v>
       </c>
       <c r="AH10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AI10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ10">
         <v>7</v>
       </c>
       <c r="AK10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AM10">
         <v>6</v>
@@ -1809,43 +1827,43 @@
         <v>10</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="X11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AD11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AE11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AF11">
         <v>9</v>
       </c>
       <c r="AG11">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AH11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI11">
         <v>7</v>
@@ -1854,13 +1872,13 @@
         <v>9</v>
       </c>
       <c r="AK11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AM11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AN11">
         <v>6</v>
@@ -1934,34 +1952,34 @@
         <v>10</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AD12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AE12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AF12">
         <v>10</v>
@@ -1982,7 +2000,7 @@
         <v>8</v>
       </c>
       <c r="AL12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AM12">
         <v>10</v>
@@ -2059,34 +2077,34 @@
         <v>5</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="X13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AD13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AE13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AF13">
         <v>5</v>
@@ -2184,46 +2202,46 @@
         <v>10</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AD14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AE14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AF14">
         <v>7</v>
       </c>
       <c r="AG14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH14">
         <v>9</v>
       </c>
       <c r="AI14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ14">
         <v>7</v>
@@ -2235,7 +2253,7 @@
         <v>5</v>
       </c>
       <c r="AM14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AN14">
         <v>5</v>
@@ -2309,34 +2327,34 @@
         <v>10</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="X15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AD15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AE15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AF15">
         <v>7</v>
@@ -2345,7 +2363,7 @@
         <v>5</v>
       </c>
       <c r="AH15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI15">
         <v>6</v>
@@ -2357,7 +2375,7 @@
         <v>6</v>
       </c>
       <c r="AL15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AM15">
         <v>5</v>
@@ -2434,37 +2452,37 @@
         <v>10</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AD16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AE16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AF16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG16">
         <v>6</v>
@@ -2476,13 +2494,13 @@
         <v>6</v>
       </c>
       <c r="AJ16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AK16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AM16">
         <v>8</v>
@@ -2559,43 +2577,43 @@
         <v>10</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AD17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AE17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AF17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AI17">
         <v>6</v>
@@ -2604,10 +2622,10 @@
         <v>6</v>
       </c>
       <c r="AK17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AM17">
         <v>7</v>
@@ -2684,55 +2702,55 @@
         <v>10</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AD18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AE18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AF18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI18">
         <v>7</v>
       </c>
       <c r="AJ18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AK18">
         <v>7</v>
       </c>
       <c r="AL18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AM18">
         <v>8</v>
@@ -2809,34 +2827,34 @@
         <v>10</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AD19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AE19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AF19">
         <v>8</v>
@@ -2934,43 +2952,43 @@
         <v>10</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AD20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AE20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AF20">
         <v>8</v>
       </c>
       <c r="AG20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI20">
         <v>7</v>
@@ -2982,7 +3000,7 @@
         <v>8</v>
       </c>
       <c r="AL20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AM20">
         <v>10</v>
@@ -3059,34 +3077,34 @@
         <v>10</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AD21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AE21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AF21">
         <v>7</v>
@@ -3101,10 +3119,10 @@
         <v>9</v>
       </c>
       <c r="AJ21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL21">
         <v>6</v>
@@ -3184,43 +3202,43 @@
         <v>10</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AD22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AE22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AF22">
         <v>7</v>
       </c>
       <c r="AG22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI22">
         <v>7</v>
@@ -3235,7 +3253,7 @@
         <v>6</v>
       </c>
       <c r="AM22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AN22">
         <v>6</v>
@@ -3309,40 +3327,40 @@
         <v>10</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AD23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AE23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AF23">
         <v>8</v>
       </c>
       <c r="AG23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH23">
         <v>9</v>
@@ -3354,16 +3372,16 @@
         <v>9</v>
       </c>
       <c r="AK23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AL23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AM23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AN23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO23">
         <v>-1</v>
@@ -3434,40 +3452,40 @@
         <v>10</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AD24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AE24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AF24">
         <v>8</v>
       </c>
       <c r="AG24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH24">
         <v>9</v>
@@ -3476,16 +3494,16 @@
         <v>8</v>
       </c>
       <c r="AJ24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AM24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AN24">
         <v>6</v>
@@ -3559,61 +3577,61 @@
         <v>10</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AD25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AE25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AF25">
         <v>8</v>
       </c>
       <c r="AG25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ25">
         <v>9</v>
       </c>
       <c r="AK25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AM25">
         <v>7</v>
       </c>
       <c r="AN25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO25">
         <v>-1</v>
@@ -3684,40 +3702,40 @@
         <v>10</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AD26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AE26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AF26">
         <v>7</v>
       </c>
       <c r="AG26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH26">
         <v>7</v>
@@ -3729,10 +3747,10 @@
         <v>7</v>
       </c>
       <c r="AK26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AL26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AM26">
         <v>7</v>
@@ -3970,10 +3988,10 @@
         <v>100</v>
       </c>
       <c r="W4">
-        <v>86.40000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="X4">
-        <v>97.5</v>
+        <v>98.3</v>
       </c>
       <c r="Y4">
         <v>100</v>
@@ -3991,7 +4009,7 @@
         <v>100</v>
       </c>
       <c r="AD4">
-        <v>95.3</v>
+        <v>96.8</v>
       </c>
       <c r="AE4">
         <v>100</v>
@@ -4062,13 +4080,13 @@
         <v>100</v>
       </c>
       <c r="V5">
-        <v>98.59999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="W5">
-        <v>86.40000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="X5">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="Y5">
         <v>100</v>
@@ -4077,16 +4095,16 @@
         <v>100</v>
       </c>
       <c r="AA5">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="AB5">
         <v>100</v>
       </c>
       <c r="AC5">
-        <v>90.59999999999999</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="AD5">
-        <v>86</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="AE5">
         <v>100</v>
@@ -4157,10 +4175,10 @@
         <v>96.7</v>
       </c>
       <c r="V6">
-        <v>98.59999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="W6">
-        <v>81.8</v>
+        <v>81.3</v>
       </c>
       <c r="X6">
         <v>100</v>
@@ -4169,22 +4187,22 @@
         <v>100</v>
       </c>
       <c r="Z6">
-        <v>98</v>
+        <v>96.3</v>
       </c>
       <c r="AA6">
-        <v>88</v>
+        <v>92.5</v>
       </c>
       <c r="AB6">
-        <v>93.8</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="AC6">
-        <v>90.59999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="AD6">
-        <v>83.7</v>
+        <v>82.5</v>
       </c>
       <c r="AE6">
-        <v>96.7</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="7" spans="1:31">
@@ -4252,34 +4270,34 @@
         <v>76.7</v>
       </c>
       <c r="V7">
-        <v>71.40000000000001</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="W7">
-        <v>77.3</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="X7">
-        <v>75</v>
+        <v>83.3</v>
       </c>
       <c r="Y7">
         <v>100</v>
       </c>
       <c r="Z7">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="AA7">
-        <v>82</v>
+        <v>88.8</v>
       </c>
       <c r="AB7">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="AC7">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="AD7">
-        <v>72.09999999999999</v>
+        <v>81</v>
       </c>
       <c r="AE7">
-        <v>76.7</v>
+        <v>79.2</v>
       </c>
     </row>
     <row r="8" spans="1:31">
@@ -4371,7 +4389,7 @@
         <v>100</v>
       </c>
       <c r="AD8">
-        <v>88.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="AE8">
         <v>100</v>
@@ -4442,34 +4460,34 @@
         <v>93.3</v>
       </c>
       <c r="V9">
-        <v>97.09999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="W9">
-        <v>86.40000000000001</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="X9">
-        <v>92.5</v>
+        <v>95</v>
       </c>
       <c r="Y9">
         <v>100</v>
       </c>
       <c r="Z9">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="AA9">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AB9">
-        <v>96.90000000000001</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="AC9">
-        <v>90.59999999999999</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="AD9">
-        <v>83.7</v>
+        <v>82.5</v>
       </c>
       <c r="AE9">
-        <v>93.3</v>
+        <v>89.59999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:31">
@@ -4537,34 +4555,34 @@
         <v>93.3</v>
       </c>
       <c r="V10">
-        <v>97.09999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="W10">
-        <v>72.7</v>
+        <v>75</v>
       </c>
       <c r="X10">
+        <v>95</v>
+      </c>
+      <c r="Y10">
+        <v>100</v>
+      </c>
+      <c r="Z10">
         <v>92.5</v>
       </c>
-      <c r="Y10">
-        <v>100</v>
-      </c>
-      <c r="Z10">
-        <v>94</v>
-      </c>
       <c r="AA10">
-        <v>88</v>
+        <v>92.5</v>
       </c>
       <c r="AB10">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="AC10">
-        <v>96.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="AD10">
-        <v>69.8</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="AE10">
-        <v>93.3</v>
+        <v>89.59999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:31">
@@ -4635,7 +4653,7 @@
         <v>100</v>
       </c>
       <c r="W11">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="X11">
         <v>100</v>
@@ -4653,13 +4671,13 @@
         <v>100</v>
       </c>
       <c r="AC11">
-        <v>96.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="AD11">
         <v>100</v>
       </c>
       <c r="AE11">
-        <v>100</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="12" spans="1:31">
@@ -4730,10 +4748,10 @@
         <v>100</v>
       </c>
       <c r="W12">
-        <v>86.40000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="X12">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="Y12">
         <v>100</v>
@@ -4751,7 +4769,7 @@
         <v>100</v>
       </c>
       <c r="AD12">
-        <v>95.3</v>
+        <v>96.8</v>
       </c>
       <c r="AE12">
         <v>100</v>
@@ -4822,34 +4840,34 @@
         <v>56.7</v>
       </c>
       <c r="V13">
-        <v>80</v>
+        <v>50.9</v>
       </c>
       <c r="W13">
-        <v>50</v>
+        <v>34.4</v>
       </c>
       <c r="X13">
-        <v>52.5</v>
+        <v>60</v>
       </c>
       <c r="Y13">
         <v>50</v>
       </c>
       <c r="Z13">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="AA13">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AB13">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="AC13">
-        <v>65.59999999999999</v>
+        <v>52.1</v>
       </c>
       <c r="AD13">
-        <v>53.5</v>
+        <v>38.1</v>
       </c>
       <c r="AE13">
-        <v>56.7</v>
+        <v>35.4</v>
       </c>
     </row>
     <row r="14" spans="1:31">
@@ -4917,34 +4935,34 @@
         <v>90</v>
       </c>
       <c r="V14">
-        <v>97.09999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="W14">
-        <v>77.3</v>
+        <v>75</v>
       </c>
       <c r="X14">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="Y14">
         <v>100</v>
       </c>
       <c r="Z14">
-        <v>96</v>
+        <v>96.3</v>
       </c>
       <c r="AA14">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AB14">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="AC14">
-        <v>90.59999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="AD14">
-        <v>79.09999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="AE14">
-        <v>90</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="15" spans="1:31">
@@ -5012,31 +5030,31 @@
         <v>83.3</v>
       </c>
       <c r="V15">
-        <v>98.59999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="W15">
-        <v>77.3</v>
+        <v>68.8</v>
       </c>
       <c r="X15">
-        <v>92.5</v>
+        <v>93.3</v>
       </c>
       <c r="Y15">
         <v>100</v>
       </c>
       <c r="Z15">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="AA15">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="AB15">
         <v>100</v>
       </c>
       <c r="AC15">
-        <v>96.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="AD15">
-        <v>83.7</v>
+        <v>82.5</v>
       </c>
       <c r="AE15">
         <v>83.3</v>
@@ -5110,10 +5128,10 @@
         <v>100</v>
       </c>
       <c r="W16">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="X16">
-        <v>97.5</v>
+        <v>98.3</v>
       </c>
       <c r="Y16">
         <v>100</v>
@@ -5122,7 +5140,7 @@
         <v>100</v>
       </c>
       <c r="AA16">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="AB16">
         <v>100</v>
@@ -5131,7 +5149,7 @@
         <v>100</v>
       </c>
       <c r="AD16">
-        <v>93</v>
+        <v>95.2</v>
       </c>
       <c r="AE16">
         <v>100</v>
@@ -5202,31 +5220,31 @@
         <v>83.3</v>
       </c>
       <c r="V17">
-        <v>81.40000000000001</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="W17">
-        <v>86.40000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="X17">
-        <v>77.5</v>
+        <v>85</v>
       </c>
       <c r="Y17">
         <v>100</v>
       </c>
       <c r="Z17">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="AA17">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="AB17">
-        <v>90.59999999999999</v>
+        <v>81.3</v>
       </c>
       <c r="AC17">
-        <v>90.59999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="AD17">
-        <v>67.40000000000001</v>
+        <v>77.8</v>
       </c>
       <c r="AE17">
         <v>83.3</v>
@@ -5297,31 +5315,31 @@
         <v>100</v>
       </c>
       <c r="V18">
-        <v>98.59999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="W18">
         <v>100</v>
       </c>
       <c r="X18">
+        <v>90</v>
+      </c>
+      <c r="Y18">
+        <v>100</v>
+      </c>
+      <c r="Z18">
+        <v>93.8</v>
+      </c>
+      <c r="AA18">
+        <v>97.5</v>
+      </c>
+      <c r="AB18">
         <v>87.5</v>
       </c>
-      <c r="Y18">
-        <v>100</v>
-      </c>
-      <c r="Z18">
-        <v>98</v>
-      </c>
-      <c r="AA18">
-        <v>96</v>
-      </c>
-      <c r="AB18">
-        <v>81.3</v>
-      </c>
       <c r="AC18">
-        <v>96.90000000000001</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="AD18">
-        <v>90.7</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="AE18">
         <v>100</v>
@@ -5395,7 +5413,7 @@
         <v>100</v>
       </c>
       <c r="W19">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="X19">
         <v>100</v>
@@ -5413,10 +5431,10 @@
         <v>100</v>
       </c>
       <c r="AC19">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="AD19">
-        <v>97.7</v>
+        <v>96.8</v>
       </c>
       <c r="AE19">
         <v>100</v>
@@ -5490,10 +5508,10 @@
         <v>100</v>
       </c>
       <c r="W20">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="X20">
-        <v>92.5</v>
+        <v>95</v>
       </c>
       <c r="Y20">
         <v>100</v>
@@ -5502,7 +5520,7 @@
         <v>100</v>
       </c>
       <c r="AA20">
-        <v>96</v>
+        <v>96.3</v>
       </c>
       <c r="AB20">
         <v>100</v>
@@ -5511,7 +5529,7 @@
         <v>100</v>
       </c>
       <c r="AD20">
-        <v>95.3</v>
+        <v>96.8</v>
       </c>
       <c r="AE20">
         <v>100</v>
@@ -5585,28 +5603,28 @@
         <v>100</v>
       </c>
       <c r="W21">
-        <v>90.90000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="X21">
-        <v>92.5</v>
+        <v>91.7</v>
       </c>
       <c r="Y21">
         <v>100</v>
       </c>
       <c r="Z21">
-        <v>94</v>
+        <v>93.8</v>
       </c>
       <c r="AA21">
-        <v>94</v>
+        <v>96.3</v>
       </c>
       <c r="AB21">
         <v>100</v>
       </c>
       <c r="AC21">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="AD21">
-        <v>93</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="AE21">
         <v>100</v>
@@ -5677,34 +5695,34 @@
         <v>93.3</v>
       </c>
       <c r="V22">
-        <v>97.09999999999999</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="W22">
-        <v>86.40000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="X22">
-        <v>92.5</v>
+        <v>93.3</v>
       </c>
       <c r="Y22">
         <v>100</v>
       </c>
       <c r="Z22">
-        <v>94</v>
+        <v>93.8</v>
       </c>
       <c r="AA22">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AB22">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="AC22">
-        <v>96.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="AD22">
-        <v>83.7</v>
+        <v>82.5</v>
       </c>
       <c r="AE22">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="23" spans="1:31">
@@ -5772,10 +5790,10 @@
         <v>93.3</v>
       </c>
       <c r="V23">
-        <v>100</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="W23">
-        <v>90.90000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="X23">
         <v>100</v>
@@ -5784,22 +5802,22 @@
         <v>100</v>
       </c>
       <c r="Z23">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="AA23">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="AB23">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="AC23">
-        <v>96.90000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="AD23">
-        <v>93</v>
+        <v>93.7</v>
       </c>
       <c r="AE23">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="24" spans="1:31">
@@ -5870,10 +5888,10 @@
         <v>100</v>
       </c>
       <c r="W24">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="X24">
-        <v>97.5</v>
+        <v>98.3</v>
       </c>
       <c r="Y24">
         <v>100</v>
@@ -5888,10 +5906,10 @@
         <v>100</v>
       </c>
       <c r="AC24">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="AD24">
-        <v>90.7</v>
+        <v>90.5</v>
       </c>
       <c r="AE24">
         <v>100</v>
@@ -5962,10 +5980,10 @@
         <v>100</v>
       </c>
       <c r="V25">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="W25">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="X25">
         <v>100</v>
@@ -5974,19 +5992,19 @@
         <v>100</v>
       </c>
       <c r="Z25">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="AA25">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="AB25">
         <v>100</v>
       </c>
       <c r="AC25">
-        <v>96.90000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="AD25">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AE25">
         <v>100</v>
@@ -6060,7 +6078,7 @@
         <v>100</v>
       </c>
       <c r="W26">
-        <v>81.8</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="X26">
         <v>100</v>
@@ -6072,16 +6090,16 @@
         <v>100</v>
       </c>
       <c r="AA26">
-        <v>98</v>
+        <v>97.5</v>
       </c>
       <c r="AB26">
-        <v>96.90000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="AC26">
         <v>100</v>
       </c>
       <c r="AD26">
-        <v>81.40000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="AE26">
         <v>100</v>
@@ -6170,7 +6188,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
         <v>52</v>
@@ -6191,7 +6209,7 @@
         <v>39.1</v>
       </c>
       <c r="H3">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6202,7 +6220,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>53</v>
@@ -6211,19 +6229,19 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E4">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F4" s="2">
-        <v>60.9</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="G4" s="2">
-        <v>39.1</v>
+        <v>30.4</v>
       </c>
       <c r="H4">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6234,7 +6252,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
         <v>54</v>
@@ -6255,7 +6273,7 @@
         <v>21.7</v>
       </c>
       <c r="H5">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6275,19 +6293,19 @@
         <v>23</v>
       </c>
       <c r="D6">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F6" s="2">
-        <v>78.3</v>
+        <v>87</v>
       </c>
       <c r="G6" s="2">
-        <v>21.7</v>
+        <v>13</v>
       </c>
       <c r="H6">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6298,7 +6316,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>56</v>
@@ -6307,19 +6325,19 @@
         <v>23</v>
       </c>
       <c r="D7">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2">
-        <v>82.59999999999999</v>
+        <v>95.7</v>
       </c>
       <c r="G7" s="2">
-        <v>17.4</v>
+        <v>4.3</v>
       </c>
       <c r="H7">
-        <v>7.7</v>
+        <v>7.1</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6330,7 +6348,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
         <v>57</v>
@@ -6339,19 +6357,19 @@
         <v>23</v>
       </c>
       <c r="D8">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" s="2">
-        <v>91.3</v>
+        <v>95.7</v>
       </c>
       <c r="G8" s="2">
-        <v>8.699999999999999</v>
+        <v>4.3</v>
       </c>
       <c r="H8">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -6371,19 +6389,19 @@
         <v>23</v>
       </c>
       <c r="D9">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" s="2">
-        <v>91.3</v>
+        <v>95.7</v>
       </c>
       <c r="G9" s="2">
-        <v>8.699999999999999</v>
+        <v>4.3</v>
       </c>
       <c r="H9">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -6394,28 +6412,28 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C10">
         <v>23</v>
       </c>
       <c r="D10">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" s="2">
-        <v>91.3</v>
+        <v>95.7</v>
       </c>
       <c r="G10" s="2">
-        <v>8.699999999999999</v>
+        <v>4.3</v>
       </c>
       <c r="H10">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -6426,10 +6444,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C11">
         <v>23</v>
@@ -6447,7 +6465,7 @@
         <v>4.3</v>
       </c>
       <c r="H11">
-        <v>7.7</v>
+        <v>6.6</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -6497,7 +6515,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6529,22 +6547,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920308</v>
+        <v>23330051920320</v>
       </c>
       <c r="B2" t="s">
         <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -6552,16 +6570,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920308</v>
+        <v>23330051920320</v>
       </c>
       <c r="B3" t="s">
         <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E3" t="s">
         <v>14</v>
@@ -6581,10 +6599,10 @@
         <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D4" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E4" t="s">
         <v>14</v>
@@ -6604,10 +6622,10 @@
         <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E5" t="s">
         <v>14</v>
@@ -6627,10 +6645,10 @@
         <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D6" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E6" t="s">
         <v>14</v>
@@ -6650,10 +6668,10 @@
         <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D7" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E7" t="s">
         <v>14</v>
@@ -6673,10 +6691,10 @@
         <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D8" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="E8" t="s">
         <v>14</v>
@@ -6696,10 +6714,10 @@
         <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D9" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E9" t="s">
         <v>14</v>
@@ -6719,10 +6737,10 @@
         <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D10" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E10" t="s">
         <v>14</v>
@@ -6742,10 +6760,10 @@
         <v>72</v>
       </c>
       <c r="C11" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D11" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E11" t="s">
         <v>14</v>
@@ -6768,7 +6786,7 @@
         <v>68</v>
       </c>
       <c r="D12" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E12" t="s">
         <v>14</v>
@@ -6782,16 +6800,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920348</v>
+        <v>23330051920308</v>
       </c>
       <c r="B13" t="s">
         <v>74</v>
       </c>
       <c r="C13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D13" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E13" t="s">
         <v>14</v>
@@ -6805,16 +6823,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920363</v>
+        <v>23330051920309</v>
       </c>
       <c r="B14" t="s">
         <v>75</v>
       </c>
       <c r="C14" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D14" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E14" t="s">
         <v>14</v>
@@ -6828,16 +6846,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920326</v>
+        <v>23330051920348</v>
       </c>
       <c r="B15" t="s">
         <v>76</v>
       </c>
       <c r="C15" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D15" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E15" t="s">
         <v>14</v>
@@ -6846,6 +6864,52 @@
         <v>51</v>
       </c>
       <c r="G15">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>23330051920363</v>
+      </c>
+      <c r="B16" t="s">
+        <v>77</v>
+      </c>
+      <c r="C16" t="s">
+        <v>90</v>
+      </c>
+      <c r="D16" t="s">
+        <v>105</v>
+      </c>
+      <c r="E16" t="s">
+        <v>14</v>
+      </c>
+      <c r="F16" t="s">
+        <v>51</v>
+      </c>
+      <c r="G16">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>23330051920326</v>
+      </c>
+      <c r="B17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C17" t="s">
+        <v>91</v>
+      </c>
+      <c r="D17" t="s">
+        <v>106</v>
+      </c>
+      <c r="E17" t="s">
+        <v>14</v>
+      </c>
+      <c r="F17" t="s">
+        <v>51</v>
+      </c>
+      <c r="G17">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/2APV - Estadisticos 20232.xlsx
+++ b/grupos/2APV - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="70">
   <si>
     <t>Materia</t>
   </si>
@@ -173,21 +173,21 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Rodríguez Román Leticia</t>
+  </si>
+  <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
+    <t>González Nuñez Veronica</t>
+  </si>
+  <si>
+    <t>Hernández Mendoza Delfina</t>
+  </si>
+  <si>
     <t>Barañon Samaniego Graciela de los Ángeles</t>
   </si>
   <si>
-    <t>Rodríguez Román Leticia</t>
-  </si>
-  <si>
-    <t>Gaspar Velazco Juan Francisco</t>
-  </si>
-  <si>
-    <t>González Nuñez Veronica</t>
-  </si>
-  <si>
-    <t>Hernández Mendoza Delfina</t>
-  </si>
-  <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
@@ -212,133 +212,22 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
     <t>ZEPAHUA</t>
   </si>
   <si>
-    <t>ACOSTA</t>
-  </si>
-  <si>
-    <t>AQUINO</t>
-  </si>
-  <si>
-    <t>BERTELY</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>IBARRA</t>
-  </si>
-  <si>
-    <t>LUCIANO</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>PELAYO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
+    <t>MARTINEZ</t>
   </si>
   <si>
     <t>APALE</t>
   </si>
   <si>
-    <t>-------------</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>GALINDO</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>ZAYAS</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
+    <t>ABRAHAN</t>
   </si>
   <si>
     <t>VALERIA</t>
-  </si>
-  <si>
-    <t>ILIAN ANELI</t>
-  </si>
-  <si>
-    <t>JURISEL</t>
-  </si>
-  <si>
-    <t>MIGUEL</t>
-  </si>
-  <si>
-    <t>DANIEL DE JESUS</t>
-  </si>
-  <si>
-    <t>MARIEL</t>
-  </si>
-  <si>
-    <t>ARMANDO</t>
-  </si>
-  <si>
-    <t>KEVIN SANTIAGO</t>
-  </si>
-  <si>
-    <t>MICHEL LEONEL</t>
-  </si>
-  <si>
-    <t>CARLOS</t>
-  </si>
-  <si>
-    <t>JUSTIN GIOVANNI</t>
-  </si>
-  <si>
-    <t>IVAN JESUS</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>AARON</t>
-  </si>
-  <si>
-    <t>YURI MONSERRAT</t>
   </si>
 </sst>
 </file>
@@ -1009,7 +898,7 @@
         <v>6</v>
       </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:41">
@@ -1134,7 +1023,7 @@
         <v>6</v>
       </c>
       <c r="AO5">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:41">
@@ -1259,7 +1148,7 @@
         <v>5</v>
       </c>
       <c r="AO6">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:41">
@@ -1384,7 +1273,7 @@
         <v>5</v>
       </c>
       <c r="AO7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:41">
@@ -1509,7 +1398,7 @@
         <v>6</v>
       </c>
       <c r="AO8">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:41">
@@ -1634,7 +1523,7 @@
         <v>5</v>
       </c>
       <c r="AO9">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:41">
@@ -1759,7 +1648,7 @@
         <v>5</v>
       </c>
       <c r="AO10">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:41">
@@ -1884,7 +1773,7 @@
         <v>6</v>
       </c>
       <c r="AO11">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:41">
@@ -2009,7 +1898,7 @@
         <v>6</v>
       </c>
       <c r="AO12">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:41">
@@ -2134,7 +2023,7 @@
         <v>5</v>
       </c>
       <c r="AO13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:41">
@@ -2259,7 +2148,7 @@
         <v>5</v>
       </c>
       <c r="AO14">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:41">
@@ -2384,7 +2273,7 @@
         <v>5</v>
       </c>
       <c r="AO15">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:41">
@@ -2509,7 +2398,7 @@
         <v>6</v>
       </c>
       <c r="AO16">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:41">
@@ -2634,7 +2523,7 @@
         <v>5</v>
       </c>
       <c r="AO17">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:41">
@@ -2759,7 +2648,7 @@
         <v>6</v>
       </c>
       <c r="AO18">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:41">
@@ -2884,7 +2773,7 @@
         <v>6</v>
       </c>
       <c r="AO19">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:41">
@@ -3009,7 +2898,7 @@
         <v>6</v>
       </c>
       <c r="AO20">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:41">
@@ -3134,7 +3023,7 @@
         <v>6</v>
       </c>
       <c r="AO21">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:41">
@@ -3259,7 +3148,7 @@
         <v>6</v>
       </c>
       <c r="AO22">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:41">
@@ -3384,7 +3273,7 @@
         <v>7</v>
       </c>
       <c r="AO23">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:41">
@@ -3509,7 +3398,7 @@
         <v>6</v>
       </c>
       <c r="AO24">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:41">
@@ -3634,7 +3523,7 @@
         <v>6</v>
       </c>
       <c r="AO25">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:41">
@@ -3759,7 +3648,7 @@
         <v>5</v>
       </c>
       <c r="AO26">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -6159,7 +6048,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
         <v>51</v>
@@ -6168,27 +6057,30 @@
         <v>23</v>
       </c>
       <c r="D2">
+        <v>14</v>
+      </c>
+      <c r="E2">
+        <v>9</v>
+      </c>
+      <c r="F2" s="2">
+        <v>60.9</v>
+      </c>
+      <c r="G2" s="2">
+        <v>39.1</v>
+      </c>
+      <c r="H2">
+        <v>5.7</v>
+      </c>
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="E2">
+      <c r="J2" s="2">
         <v>0</v>
-      </c>
-      <c r="F2" s="2">
-        <v>0</v>
-      </c>
-      <c r="G2" s="2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>23</v>
-      </c>
-      <c r="J2" s="2">
-        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>52</v>
@@ -6197,19 +6089,19 @@
         <v>23</v>
       </c>
       <c r="D3">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F3" s="2">
-        <v>60.9</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="G3" s="2">
-        <v>39.1</v>
+        <v>30.4</v>
       </c>
       <c r="H3">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6220,7 +6112,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
         <v>53</v>
@@ -6229,19 +6121,19 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4" s="2">
-        <v>69.59999999999999</v>
+        <v>78.3</v>
       </c>
       <c r="G4" s="2">
-        <v>30.4</v>
+        <v>21.7</v>
       </c>
       <c r="H4">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6252,7 +6144,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
         <v>54</v>
@@ -6261,19 +6153,19 @@
         <v>23</v>
       </c>
       <c r="D5">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F5" s="2">
-        <v>78.3</v>
+        <v>87</v>
       </c>
       <c r="G5" s="2">
-        <v>21.7</v>
+        <v>13</v>
       </c>
       <c r="H5">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6284,7 +6176,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
         <v>55</v>
@@ -6293,19 +6185,19 @@
         <v>23</v>
       </c>
       <c r="D6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6" s="2">
-        <v>87</v>
+        <v>91.3</v>
       </c>
       <c r="G6" s="2">
-        <v>13</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H6">
-        <v>7.2</v>
+        <v>9.6</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6515,7 +6407,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6547,22 +6439,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920320</v>
+        <v>23330051920365</v>
       </c>
       <c r="B2" t="s">
         <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -6570,347 +6462,48 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920320</v>
+        <v>23330051920365</v>
       </c>
       <c r="B3" t="s">
         <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="D3" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F3" t="s">
         <v>51</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920322</v>
+        <v>23330051920320</v>
       </c>
       <c r="B4" t="s">
         <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="D4" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F4" t="s">
         <v>51</v>
       </c>
       <c r="G4">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>23330051920281</v>
-      </c>
-      <c r="B5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C5" t="s">
-        <v>81</v>
-      </c>
-      <c r="D5" t="s">
-        <v>94</v>
-      </c>
-      <c r="E5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" t="s">
-        <v>51</v>
-      </c>
-      <c r="G5">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>23330051920284</v>
-      </c>
-      <c r="B6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C6" t="s">
-        <v>82</v>
-      </c>
-      <c r="D6" t="s">
-        <v>95</v>
-      </c>
-      <c r="E6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" t="s">
-        <v>51</v>
-      </c>
-      <c r="G6">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>23330051920285</v>
-      </c>
-      <c r="B7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" t="s">
-        <v>83</v>
-      </c>
-      <c r="D7" t="s">
-        <v>96</v>
-      </c>
-      <c r="E7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" t="s">
-        <v>51</v>
-      </c>
-      <c r="G7">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>23330051920292</v>
-      </c>
-      <c r="B8" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8" t="s">
-        <v>84</v>
-      </c>
-      <c r="D8" t="s">
-        <v>97</v>
-      </c>
-      <c r="E8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" t="s">
-        <v>51</v>
-      </c>
-      <c r="G8">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>23330051920295</v>
-      </c>
-      <c r="B9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C9" t="s">
-        <v>85</v>
-      </c>
-      <c r="D9" t="s">
-        <v>98</v>
-      </c>
-      <c r="E9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" t="s">
-        <v>51</v>
-      </c>
-      <c r="G9">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>23330051920296</v>
-      </c>
-      <c r="B10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C10" t="s">
-        <v>86</v>
-      </c>
-      <c r="D10" t="s">
-        <v>99</v>
-      </c>
-      <c r="E10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" t="s">
-        <v>51</v>
-      </c>
-      <c r="G10">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>23330051920299</v>
-      </c>
-      <c r="B11" t="s">
-        <v>72</v>
-      </c>
-      <c r="C11" t="s">
-        <v>84</v>
-      </c>
-      <c r="D11" t="s">
-        <v>100</v>
-      </c>
-      <c r="E11" t="s">
-        <v>14</v>
-      </c>
-      <c r="F11" t="s">
-        <v>51</v>
-      </c>
-      <c r="G11">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>23330051920301</v>
-      </c>
-      <c r="B12" t="s">
-        <v>73</v>
-      </c>
-      <c r="C12" t="s">
-        <v>68</v>
-      </c>
-      <c r="D12" t="s">
-        <v>101</v>
-      </c>
-      <c r="E12" t="s">
-        <v>14</v>
-      </c>
-      <c r="F12" t="s">
-        <v>51</v>
-      </c>
-      <c r="G12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>23330051920308</v>
-      </c>
-      <c r="B13" t="s">
-        <v>74</v>
-      </c>
-      <c r="C13" t="s">
-        <v>87</v>
-      </c>
-      <c r="D13" t="s">
-        <v>102</v>
-      </c>
-      <c r="E13" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" t="s">
-        <v>51</v>
-      </c>
-      <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>23330051920309</v>
-      </c>
-      <c r="B14" t="s">
-        <v>75</v>
-      </c>
-      <c r="C14" t="s">
-        <v>88</v>
-      </c>
-      <c r="D14" t="s">
-        <v>103</v>
-      </c>
-      <c r="E14" t="s">
-        <v>14</v>
-      </c>
-      <c r="F14" t="s">
-        <v>51</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>23330051920348</v>
-      </c>
-      <c r="B15" t="s">
-        <v>76</v>
-      </c>
-      <c r="C15" t="s">
-        <v>89</v>
-      </c>
-      <c r="D15" t="s">
-        <v>104</v>
-      </c>
-      <c r="E15" t="s">
-        <v>14</v>
-      </c>
-      <c r="F15" t="s">
-        <v>51</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>23330051920363</v>
-      </c>
-      <c r="B16" t="s">
-        <v>77</v>
-      </c>
-      <c r="C16" t="s">
-        <v>90</v>
-      </c>
-      <c r="D16" t="s">
-        <v>105</v>
-      </c>
-      <c r="E16" t="s">
-        <v>14</v>
-      </c>
-      <c r="F16" t="s">
-        <v>51</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>23330051920326</v>
-      </c>
-      <c r="B17" t="s">
-        <v>78</v>
-      </c>
-      <c r="C17" t="s">
-        <v>91</v>
-      </c>
-      <c r="D17" t="s">
-        <v>106</v>
-      </c>
-      <c r="E17" t="s">
-        <v>14</v>
-      </c>
-      <c r="F17" t="s">
-        <v>51</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
